--- a/Excel/TaskPositionConfig.xlsx
+++ b/Excel/TaskPositionConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B127879C-9128-4136-A630-2FF41FD7410C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28080" windowHeight="14085"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TaskPositionProto" sheetId="1" r:id="rId1"/>
@@ -14,18 +20,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>dreamsummit</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>dreamsummit:</t>
@@ -34,6 +41,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -43,6 +51,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>先判定是否有移动坐标点,如果有移动坐标点,则直接读取,不用读取后面的坐标点</t>
@@ -54,15 +63,15 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Item_Template" type="4" background="1" refreshedVersion="2" saveData="1">
-    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Item_Template" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="193">
   <si>
     <t>Id</t>
   </si>
@@ -102,6 +111,7 @@
         <sz val="10"/>
         <color theme="0"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>s</t>
@@ -111,6 +121,7 @@
         <sz val="10"/>
         <color theme="0"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>tring</t>
@@ -560,18 +571,113 @@
   <si>
     <t>最终BOSS</t>
   </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapName_EN</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greenwood Town</t>
+  </si>
+  <si>
+    <t>Level 1 of the Mine Shaft</t>
+  </si>
+  <si>
+    <t>Second floor of the mine</t>
+  </si>
+  <si>
+    <t>Green Leaf Outskirts</t>
+  </si>
+  <si>
+    <t>Green Leaf Forest</t>
+  </si>
+  <si>
+    <t>Death Cave</t>
+  </si>
+  <si>
+    <t>The first floor of the ancient tomb</t>
+  </si>
+  <si>
+    <t>Second floor of the tomb</t>
+  </si>
+  <si>
+    <t>Desert of Scorching Heat</t>
+  </si>
+  <si>
+    <t>Curse Ruins</t>
+  </si>
+  <si>
+    <t>Floor 1 of the Dungeon</t>
+  </si>
+  <si>
+    <t>Second floor of the dungeon</t>
+  </si>
+  <si>
+    <t>Frozen Town</t>
+  </si>
+  <si>
+    <t>Frozen Forest</t>
+  </si>
+  <si>
+    <t>Frozen Fortress</t>
+  </si>
+  <si>
+    <t>Thousand-needle forest</t>
+  </si>
+  <si>
+    <t>Frozen Path</t>
+  </si>
+  <si>
+    <t>Frozen Demon穴</t>
+  </si>
+  <si>
+    <t>Dusk Town</t>
+  </si>
+  <si>
+    <t>The dusk outskirts</t>
+  </si>
+  <si>
+    <t>Dusk Forest</t>
+  </si>
+  <si>
+    <t>Dusk Mine Level 1</t>
+  </si>
+  <si>
+    <t>Second floor of the Twilight Mine</t>
+  </si>
+  <si>
+    <t>Crack Stone Canyon</t>
+  </si>
+  <si>
+    <t>Hell Rift Valley</t>
+  </si>
+  <si>
+    <t>Dark Town</t>
+  </si>
+  <si>
+    <t>Strange path</t>
+  </si>
+  <si>
+    <t>Corrosive Land</t>
+  </si>
+  <si>
+    <t>The first floor of the Dark Corridor</t>
+  </si>
+  <si>
+    <t>Dark Corridor, 3rd floor</t>
+  </si>
+  <si>
+    <t>Heart of Darkness</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,12 +690,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -597,125 +705,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -723,30 +713,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -754,18 +737,37 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -786,198 +788,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14993743705557422"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1052,256 +868,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1333,62 +907,24 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 3" xfId="50"/>
-    <cellStyle name="常规 4" xfId="51"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1416,7 +952,7 @@
     </xsd:schema>
   </Schema>
   <Map ID="1" Name="DateArea_映射" RootElement="DateArea" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true">
-    <DataBinding ConnectionID="1" FileBinding="true" DataBindingLoadMode="1"/>
+    <DataBinding FileBinding="true" ConnectionID="1" DataBindingLoadMode="1"/>
   </Map>
 </MapInfo>
 </file>
@@ -1702,24 +1238,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:H198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I198"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="23.125" customWidth="1"/>
-    <col min="5" max="5" width="39.375" customWidth="1"/>
-    <col min="6" max="6" width="30.375" customWidth="1"/>
-    <col min="7" max="7" width="56.75" customWidth="1"/>
+    <col min="4" max="5" width="23.125" customWidth="1"/>
+    <col min="6" max="6" width="39.375" customWidth="1"/>
+    <col min="7" max="7" width="30.375" customWidth="1"/>
+    <col min="8" max="8" width="56.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1"/>
-    <row r="3" ht="20.1" customHeight="1" spans="3:7">
+    <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E2" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1727,16 +1267,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:7">
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,16 +1287,19 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:7">
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1761,16 +1307,19 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:8">
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5">
@@ -1779,20 +1328,23 @@
       <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="5">
         <v>10001</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:8">
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5">
@@ -1801,20 +1353,23 @@
       <c r="D7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="5">
         <v>10001</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="1:8">
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5">
@@ -1823,20 +1378,23 @@
       <c r="D8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="5">
         <v>10001</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:8">
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5">
@@ -1845,20 +1403,23 @@
       <c r="D9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" s="5">
         <v>10001</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:8">
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5">
@@ -1867,20 +1428,23 @@
       <c r="D10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" s="5">
         <v>10001</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:8">
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5">
@@ -1889,20 +1453,23 @@
       <c r="D11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="5">
         <v>10001</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:8">
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5">
@@ -1911,20 +1478,23 @@
       <c r="D12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="5">
         <v>10001</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:8">
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5">
@@ -1933,20 +1503,23 @@
       <c r="D13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="5">
         <v>10001</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:8">
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5">
@@ -1955,20 +1528,23 @@
       <c r="D14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="5">
         <v>10001</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:8">
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5">
@@ -1977,20 +1553,23 @@
       <c r="D15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="5">
         <v>10001</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:8">
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5">
@@ -1999,20 +1578,23 @@
       <c r="D16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" s="5">
         <v>10002</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:8">
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5">
@@ -2021,20 +1603,23 @@
       <c r="D17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="5">
         <v>10002</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:8">
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5">
@@ -2043,20 +1628,23 @@
       <c r="D18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" s="5">
         <v>10002</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:8">
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5">
@@ -2065,20 +1653,23 @@
       <c r="D19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="5">
         <v>10002</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:8">
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5">
@@ -2087,20 +1678,23 @@
       <c r="D20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="5">
         <v>10002</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:8">
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5">
@@ -2109,20 +1703,23 @@
       <c r="D21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="5">
         <v>10002</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:8">
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5">
@@ -2131,20 +1728,23 @@
       <c r="D22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="5">
         <v>10003</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="H22" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:8">
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="5">
@@ -2153,20 +1753,23 @@
       <c r="D23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="5">
         <v>10003</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="1:8">
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5">
@@ -2175,20 +1778,23 @@
       <c r="D24" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="5">
         <v>10003</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:8">
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5">
@@ -2197,20 +1803,23 @@
       <c r="D25" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="5">
         <v>10003</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:8">
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="6">
@@ -2219,20 +1828,23 @@
       <c r="D26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="6">
         <v>10003</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="1:8">
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="6">
@@ -2241,180 +1853,207 @@
       <c r="D27" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" s="6">
         <v>10004</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="H27" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="I27" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="3:8">
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="6">
         <v>100302</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" s="6">
         <v>10004</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="3:8">
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="6">
         <v>100303</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" s="6">
         <v>10004</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:8">
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="6">
         <v>100304</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="6">
         <v>10004</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:8">
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="6">
         <v>100305</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="6">
         <v>10004</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:8">
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="6">
         <v>100401</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" s="6">
         <v>10005</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:8">
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="6">
         <v>100402</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="6">
         <v>10005</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:8">
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6">
         <v>100403</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" s="6">
         <v>10005</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:8">
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6">
         <v>100404</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35" s="6">
         <v>10005</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="H35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="I35" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="1:8">
+    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="6">
@@ -2423,280 +2062,322 @@
       <c r="D36" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="6">
         <v>10006</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:8">
+    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="6">
         <v>100502</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" s="6">
         <v>10006</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:8">
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="6">
         <v>100503</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" s="6">
         <v>10006</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:8">
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="6">
         <v>100504</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="6">
         <v>10006</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:8">
+    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="6">
         <v>100505</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F40" s="6">
         <v>10006</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:8">
+    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="6">
         <v>100601</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41" s="10">
         <v>10007</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:8">
+    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
         <v>100602</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F42" s="10">
         <v>10007</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="H42" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="I42" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:8">
+    <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
         <v>100603</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F43" s="10">
         <v>10007</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:8">
+    <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
         <v>100604</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="10">
         <v>10007</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:8">
+    <row r="45" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
         <v>100701</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" s="10">
         <v>10008</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:8">
+    <row r="46" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
         <v>100702</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46" s="10">
         <v>10008</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="H46" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:8">
+    <row r="47" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
         <v>100703</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" s="10">
         <v>10008</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:8">
+    <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
         <v>100704</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F48" s="10">
         <v>10008</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="49" ht="20.1" customHeight="1" spans="3:8">
+    <row r="49" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="6">
         <v>100705</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F49" s="10">
         <v>10008</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="G49" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" ht="20.1" customHeight="1" spans="1:8">
+    <row r="50" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5">
@@ -2705,20 +2386,23 @@
       <c r="D50" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" s="5">
         <v>20001</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="1:8">
+    <row r="51" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="5">
@@ -2727,20 +2411,23 @@
       <c r="D51" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51" s="5">
         <v>20001</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="52" ht="20.1" customHeight="1" spans="1:8">
+    <row r="52" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="5">
@@ -2749,20 +2436,23 @@
       <c r="D52" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F52" s="5">
         <v>20001</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="G52" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="53" ht="20.1" customHeight="1" spans="1:8">
+    <row r="53" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="5">
@@ -2771,20 +2461,23 @@
       <c r="D53" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F53" s="5">
         <v>20001</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G53" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" spans="1:8">
+    <row r="54" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5">
@@ -2793,20 +2486,23 @@
       <c r="D54" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="5">
         <v>20002</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="G54" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="8" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" ht="20.1" customHeight="1" spans="1:8">
+    <row r="55" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="5">
@@ -2815,20 +2511,23 @@
       <c r="D55" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F55" s="5">
         <v>20002</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G55" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="56" ht="20.1" customHeight="1" spans="1:8">
+    <row r="56" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5">
@@ -2837,20 +2536,23 @@
       <c r="D56" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" s="5">
         <v>20002</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="57" ht="20.1" customHeight="1" spans="1:8">
+    <row r="57" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5">
@@ -2859,20 +2561,23 @@
       <c r="D57" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F57" s="5">
         <v>20002</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" s="8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="58" ht="20.1" customHeight="1" spans="1:8">
+    <row r="58" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="5">
@@ -2881,100 +2586,115 @@
       <c r="D58" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F58" s="5">
         <v>20003</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="G58" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="59" ht="20.1" customHeight="1" spans="3:8">
+    <row r="59" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="5">
         <v>200202</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F59" s="5">
         <v>20003</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="8" t="s">
+      <c r="H59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="60" ht="20.1" customHeight="1" spans="3:8">
+    <row r="60" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="5">
         <v>200203</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F60" s="5">
         <v>20003</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="G60" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G60" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" s="8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="61" ht="20.1" customHeight="1" spans="3:8">
+    <row r="61" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="5">
         <v>200204</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F61" s="5">
         <v>20003</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:8">
+    <row r="62" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="5">
         <v>200205</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F62" s="5">
         <v>20003</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" s="8" t="s">
+      <c r="H62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="63" ht="20.1" customHeight="1" spans="1:8">
+    <row r="63" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5">
@@ -2983,120 +2703,138 @@
       <c r="D63" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F63" s="5">
         <v>20004</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="64" ht="20.1" customHeight="1" spans="3:8">
+    <row r="64" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="5">
         <v>200302</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F64" s="5">
         <v>20004</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="G64" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:8">
+    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="5">
         <v>200303</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F65" s="5">
         <v>20004</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:8">
+    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="5">
         <v>200304</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F66" s="5">
         <v>20004</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="G66" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" s="8" t="s">
+      <c r="H66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:8">
+    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="5">
         <v>200401</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F67" s="5">
         <v>20005</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="8" t="s">
+      <c r="H67" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:8">
+    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="5">
         <v>200402</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F68" s="5">
         <v>20005</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="G68" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="8" t="s">
+      <c r="H68" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="69" ht="20.1" customHeight="1" spans="1:8">
+    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5">
@@ -3105,20 +2843,23 @@
       <c r="D69" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F69" s="5">
         <v>30001</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="G69" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="70" ht="20.1" customHeight="1" spans="1:8">
+    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="5">
@@ -3127,20 +2868,23 @@
       <c r="D70" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" s="5">
         <v>30001</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="G70" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="71" ht="20.1" customHeight="1" spans="1:8">
+    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="5">
@@ -3149,20 +2893,23 @@
       <c r="D71" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E71" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F71" s="5">
         <v>30001</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="G71" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="8" t="s">
+      <c r="H71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="72" ht="20.1" customHeight="1" spans="1:8">
+    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="5">
@@ -3171,20 +2918,23 @@
       <c r="D72" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" s="5">
         <v>30001</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="G72" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="73" ht="20.1" customHeight="1" spans="1:8">
+    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5">
@@ -3193,20 +2943,23 @@
       <c r="D73" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" s="5">
         <v>30002</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="G73" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G73" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="8" t="s">
+      <c r="H73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="74" ht="20.1" customHeight="1" spans="1:8">
+    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5">
@@ -3215,20 +2968,23 @@
       <c r="D74" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E74" s="5">
+      <c r="E74" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" s="5">
         <v>30002</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="G74" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="75" ht="20.1" customHeight="1" spans="1:8">
+    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5">
@@ -3237,20 +2993,23 @@
       <c r="D75" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E75" s="5">
+      <c r="E75" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" s="5">
         <v>30002</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="G75" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G75" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="76" ht="20.1" customHeight="1" spans="1:8">
+    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5">
@@ -3259,20 +3018,23 @@
       <c r="D76" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" s="5">
         <v>30002</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="G76" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="H76" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H76" s="8" t="s">
+      <c r="I76" s="8" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" ht="20.1" customHeight="1" spans="1:8">
+    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5">
@@ -3281,20 +3043,23 @@
       <c r="D77" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E77" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F77" s="5">
         <v>30003</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G77" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="78" ht="20.1" customHeight="1" spans="1:8">
+    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="5">
@@ -3303,60 +3068,69 @@
       <c r="D78" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F78" s="5">
         <v>30003</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="G78" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:8">
+    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="5">
         <v>300303</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F79" s="5">
         <v>30003</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="G79" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:8">
+    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="5">
         <v>300304</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F80" s="5">
         <v>30003</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="G80" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G80" s="7" t="s">
+      <c r="H80" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="I80" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="81" ht="20.1" customHeight="1" spans="1:8">
+    <row r="81" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="5">
@@ -3365,20 +3139,23 @@
       <c r="D81" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F81" s="5">
         <v>30004</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="G81" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G81" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="82" ht="20.1" customHeight="1" spans="1:8">
+    <row r="82" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="5">
@@ -3387,20 +3164,23 @@
       <c r="D82" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="5">
         <v>30004</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="G82" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G82" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="83" ht="20.1" customHeight="1" spans="1:8">
+    <row r="83" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="5">
@@ -3409,20 +3189,23 @@
       <c r="D83" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83" s="5">
         <v>30004</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="G83" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G83" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" s="8" t="s">
+      <c r="H83" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="1:8">
+    <row r="84" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="5">
@@ -3431,1219 +3214,1393 @@
       <c r="D84" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E84" s="5">
+      <c r="E84" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F84" s="5">
         <v>30004</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="G84" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G84" s="7" t="s">
+      <c r="H84" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H84" s="8" t="s">
+      <c r="I84" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:8">
+    <row r="85" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C85" s="5">
         <v>300501</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F85" s="5">
         <v>30005</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="G85" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" s="8" t="s">
+      <c r="H85" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:8">
+    <row r="86" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C86" s="5">
         <v>300502</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E86" s="5">
+      <c r="E86" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F86" s="5">
         <v>30005</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="G86" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H86" s="8" t="s">
+      <c r="H86" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:8">
+    <row r="87" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C87" s="5">
         <v>300503</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E87" s="5">
+      <c r="E87" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F87" s="5">
         <v>30005</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="8" t="s">
+      <c r="H87" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:8">
+    <row r="88" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C88" s="5">
         <v>300504</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E88" s="5">
+      <c r="E88" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F88" s="5">
         <v>30005</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="G88" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" s="8" t="s">
+      <c r="H88" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I88" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:8">
+    <row r="89" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C89" s="5">
         <v>300505</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E89" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F89" s="5">
         <v>30005</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="G89" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G89" s="7" t="s">
+      <c r="H89" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H89" s="8" t="s">
+      <c r="I89" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:8">
+    <row r="90" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C90" s="10">
         <v>300601</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F90" s="5">
         <v>30006</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="G90" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G90" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" s="8" t="s">
+      <c r="H90" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I90" s="8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:8">
+    <row r="91" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C91" s="10">
         <v>300602</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F91" s="5">
         <v>30006</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="G91" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G91" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" s="8" t="s">
+      <c r="H91" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I91" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:8">
+    <row r="92" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C92" s="10">
         <v>300603</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E92" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F92" s="5">
         <v>30006</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="G92" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H92" s="8" t="s">
+      <c r="H92" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:8">
+    <row r="93" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C93" s="10">
         <v>300604</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F93" s="5">
         <v>30006</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="G93" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G93" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" s="8" t="s">
+      <c r="H93" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:8">
+    <row r="94" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C94" s="10">
         <v>300605</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E94" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F94" s="5">
         <v>30006</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="G94" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G94" s="7" t="s">
+      <c r="H94" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="H94" s="8" t="s">
+      <c r="I94" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:8">
+    <row r="95" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C95" s="10">
         <v>400101</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E95" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F95" s="5">
         <v>40001</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="G95" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G95" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H95" s="8" t="s">
+      <c r="H95" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:8">
+    <row r="96" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C96" s="10">
         <v>400102</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E96" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F96" s="5">
         <v>40001</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="G96" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G96" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H96" s="8" t="s">
+      <c r="H96" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:8">
+    <row r="97" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C97" s="10">
         <v>400103</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E97" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F97" s="5">
         <v>40001</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="G97" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G97" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H97" s="8" t="s">
+      <c r="H97" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:8">
+    <row r="98" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C98" s="10">
         <v>400104</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E98" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F98" s="5">
         <v>40001</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="G98" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H98" s="8" t="s">
+      <c r="H98" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:8">
+    <row r="99" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C99" s="10">
         <v>400105</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F99" s="5">
         <v>40001</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="G99" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G99" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H99" s="8" t="s">
+      <c r="H99" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:8">
+    <row r="100" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C100" s="10">
         <v>400201</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E100" s="10">
+      <c r="E100" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F100" s="10">
         <v>40002</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="G100" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G100" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="8" t="s">
+      <c r="H100" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:8">
+    <row r="101" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C101" s="10">
         <v>400202</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E101" s="10">
+      <c r="E101" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F101" s="10">
         <v>40002</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="G101" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H101" s="8" t="s">
+      <c r="H101" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:8">
+    <row r="102" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C102" s="10">
         <v>400203</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E102" s="10">
+      <c r="E102" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F102" s="10">
         <v>40002</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="G102" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="H102" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H102" s="8" t="s">
+      <c r="I102" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:8">
+    <row r="103" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C103" s="10">
         <v>400204</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E103" s="10">
+      <c r="E103" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F103" s="10">
         <v>40002</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="G103" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H103" s="8" t="s">
+      <c r="H103" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:8">
+    <row r="104" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C104" s="10">
         <v>400301</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E104" s="10">
+      <c r="E104" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F104" s="10">
         <v>40003</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="G104" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G104" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H104" s="8" t="s">
+      <c r="H104" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:8">
+    <row r="105" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C105" s="10">
         <v>400302</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E105" s="10">
+      <c r="E105" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F105" s="10">
         <v>40003</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="G105" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G105" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H105" s="8" t="s">
+      <c r="H105" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:8">
+    <row r="106" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C106" s="10">
         <v>400303</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E106" s="10">
+      <c r="E106" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F106" s="10">
         <v>40003</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="G106" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G106" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H106" s="8" t="s">
+      <c r="H106" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I106" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:8">
+    <row r="107" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C107" s="10">
         <v>400304</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E107" s="10">
+      <c r="E107" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F107" s="10">
         <v>40003</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="G107" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G107" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H107" s="8" t="s">
+      <c r="H107" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" s="8" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:8">
+    <row r="108" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C108" s="10">
         <v>400305</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E108" s="10">
+      <c r="E108" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F108" s="10">
         <v>40003</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="G108" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="H108" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H108" s="8" t="s">
+      <c r="I108" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:8">
+    <row r="109" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C109" s="10">
         <v>400401</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E109" s="10">
+      <c r="E109" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F109" s="10">
         <v>40004</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="G109" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="H109" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="H109" s="8" t="s">
+      <c r="I109" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:8">
+    <row r="110" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C110" s="10">
         <v>400402</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E110" s="10">
+      <c r="E110" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F110" s="10">
         <v>40004</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="G110" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G110" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" s="8" t="s">
+      <c r="H110" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I110" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:8">
+    <row r="111" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C111" s="10">
         <v>400403</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E111" s="10">
+      <c r="E111" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F111" s="10">
         <v>40004</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="G111" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G111" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H111" s="8" t="s">
+      <c r="H111" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" s="8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:8">
+    <row r="112" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="10">
         <v>400404</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E112" s="10">
+      <c r="E112" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F112" s="10">
         <v>40004</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="G112" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G112" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" s="8" t="s">
+      <c r="H112" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:8">
+    <row r="113" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="10">
         <v>400405</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E113" s="10">
+      <c r="E113" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F113" s="10">
         <v>40004</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="G113" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H113" s="8" t="s">
+      <c r="H113" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I113" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:8">
+    <row r="114" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="10">
         <v>400406</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E114" s="10">
+      <c r="E114" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F114" s="10">
         <v>40004</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="G114" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" s="8" t="s">
+      <c r="H114" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:8">
+    <row r="115" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="10">
         <v>400501</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E115" s="10">
+      <c r="E115" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F115" s="10">
         <v>40005</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="G115" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H115" s="8" t="s">
+      <c r="H115" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I115" s="8" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:8">
+    <row r="116" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C116" s="10">
         <v>400502</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E116" s="10">
+      <c r="E116" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F116" s="10">
         <v>40005</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="G116" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G116" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" s="8" t="s">
+      <c r="H116" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I116" s="8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:8">
+    <row r="117" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="10">
         <v>400503</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E117" s="10">
+      <c r="E117" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F117" s="10">
         <v>40005</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="G117" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G117" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H117" s="8" t="s">
+      <c r="H117" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:8">
+    <row r="118" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="10">
         <v>400504</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E118" s="10">
+      <c r="E118" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F118" s="10">
         <v>40005</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="G118" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G118" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" s="8" t="s">
+      <c r="H118" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:8">
+    <row r="119" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="10">
         <v>400601</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E119" s="10">
+      <c r="E119" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F119" s="10">
         <v>40006</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="G119" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G119" s="7" t="s">
+      <c r="H119" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="H119" s="8" t="s">
+      <c r="I119" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:8">
+    <row r="120" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C120" s="10">
         <v>400602</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E120" s="10">
+      <c r="E120" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F120" s="10">
         <v>40006</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="G120" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G120" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" s="8" t="s">
+      <c r="H120" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:8">
+    <row r="121" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C121" s="10">
         <v>400603</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E121" s="10">
+      <c r="E121" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F121" s="10">
         <v>40006</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="G121" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G121" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H121" s="8" t="s">
+      <c r="H121" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:8">
+    <row r="122" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C122" s="10">
         <v>400701</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E122" s="10">
+      <c r="E122" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F122" s="10">
         <v>40007</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="G122" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G122" s="7" t="s">
+      <c r="H122" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="H122" s="8" t="s">
+      <c r="I122" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:8">
+    <row r="123" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C123" s="10">
         <v>400702</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F123" s="10">
         <v>40007</v>
       </c>
-      <c r="F123" s="5" t="s">
+      <c r="G123" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G123" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="8" t="s">
+      <c r="H123" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="124" ht="20.1" customHeight="1" spans="3:8">
+    <row r="124" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C124" s="10">
         <v>400703</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E124" s="10">
+      <c r="E124" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F124" s="10">
         <v>40007</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="G124" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G124" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="8" t="s">
+      <c r="H124" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="125" ht="20.1" customHeight="1" spans="3:8">
+    <row r="125" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C125" s="10">
         <v>500101</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E125" s="10">
+      <c r="E125" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F125" s="10">
         <v>50001</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="G125" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G125" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H125" s="8" t="s">
+      <c r="H125" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="126" ht="20.1" customHeight="1" spans="3:8">
+    <row r="126" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C126" s="10">
         <v>500102</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E126" s="10">
+      <c r="E126" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F126" s="10">
         <v>50001</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="G126" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G126" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="8" t="s">
+      <c r="H126" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="127" ht="20.1" customHeight="1" spans="3:8">
+    <row r="127" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C127" s="10">
         <v>500103</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E127" s="10">
+      <c r="E127" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F127" s="10">
         <v>50001</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="G127" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G127" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H127" s="8" t="s">
+      <c r="H127" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I127" s="8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="128" ht="20.1" customHeight="1" spans="3:8">
+    <row r="128" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C128" s="10">
         <v>500104</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F128" s="10">
         <v>50001</v>
       </c>
-      <c r="F128" s="5" t="s">
+      <c r="G128" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G128" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H128" s="8" t="s">
+      <c r="H128" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" s="8" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="129" ht="20.1" customHeight="1" spans="3:8">
+    <row r="129" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C129" s="10">
         <v>500201</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E129" s="10">
+      <c r="E129" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F129" s="10">
         <v>50002</v>
       </c>
-      <c r="F129" s="5" t="s">
+      <c r="G129" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G129" s="7" t="s">
+      <c r="H129" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="H129" s="8" t="s">
+      <c r="I129" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="130" ht="20.1" customHeight="1" spans="3:8">
+    <row r="130" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C130" s="10">
         <v>500202</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E130" s="10">
+      <c r="E130" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F130" s="10">
         <v>50002</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="G130" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G130" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H130" s="8" t="s">
+      <c r="H130" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I130" s="8" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="131" ht="20.1" customHeight="1" spans="3:8">
+    <row r="131" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C131" s="10">
         <v>500203</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E131" s="10">
+      <c r="E131" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F131" s="10">
         <v>50002</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="G131" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G131" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H131" s="8" t="s">
+      <c r="H131" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I131" s="8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="132" ht="20.1" customHeight="1" spans="3:8">
+    <row r="132" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C132" s="10">
         <v>500204</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E132" s="10">
+      <c r="E132" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F132" s="10">
         <v>50002</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="G132" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G132" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H132" s="8" t="s">
+      <c r="H132" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="133" ht="20.1" customHeight="1" spans="3:8">
+    <row r="133" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C133" s="10">
         <v>500205</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E133" s="10">
+      <c r="E133" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F133" s="10">
         <v>50002</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="G133" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G133" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H133" s="8" t="s">
+      <c r="H133" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I133" s="8" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="134" ht="20.1" customHeight="1" spans="3:8">
+    <row r="134" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C134" s="10">
         <v>500301</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E134" s="10">
+      <c r="E134" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F134" s="10">
         <v>50003</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="G134" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G134" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H134" s="8" t="s">
+      <c r="H134" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I134" s="8" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="135" ht="20.1" customHeight="1" spans="3:8">
+    <row r="135" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C135" s="10">
         <v>500302</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E135" s="10">
+      <c r="E135" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F135" s="10">
         <v>50003</v>
       </c>
-      <c r="F135" s="5" t="s">
+      <c r="G135" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G135" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H135" s="8" t="s">
+      <c r="H135" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I135" s="8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="136" ht="20.1" customHeight="1" spans="3:8">
+    <row r="136" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C136" s="10">
         <v>500303</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E136" s="10">
+      <c r="E136" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F136" s="10">
         <v>50003</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="G136" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G136" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H136" s="8" t="s">
+      <c r="H136" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I136" s="8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="137" ht="20.1" customHeight="1" spans="3:8">
+    <row r="137" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C137" s="10">
         <v>500304</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E137" s="10">
+      <c r="E137" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F137" s="10">
         <v>50003</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="G137" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G137" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H137" s="8" t="s">
+      <c r="H137" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" s="8" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="138" ht="20.1" customHeight="1" spans="3:8">
+    <row r="138" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C138" s="10">
         <v>500401</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E138" s="10">
+      <c r="E138" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F138" s="10">
         <v>50004</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="G138" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G138" s="7" t="s">
+      <c r="H138" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="H138" s="8" t="s">
+      <c r="I138" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="139" ht="20.1" customHeight="1" spans="3:8">
+    <row r="139" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C139" s="10">
         <v>500601</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E139" s="10">
+      <c r="E139" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F139" s="10">
         <v>50006</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="G139" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G139" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H139" s="8" t="s">
+      <c r="H139" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I139" s="8" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="140" ht="20.1" customHeight="1" spans="3:8">
+    <row r="140" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C140" s="10">
         <v>500602</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E140" s="10">
+      <c r="E140" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F140" s="10">
         <v>50006</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="G140" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G140" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H140" s="8" t="s">
+      <c r="H140" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I140" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="141" ht="20.1" customHeight="1" spans="3:8">
+    <row r="141" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C141" s="10">
         <v>500701</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E141" s="10">
+      <c r="E141" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F141" s="10">
         <v>50007</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="G141" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G141" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H141" s="8" t="s">
+      <c r="H141" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I141" s="8" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="142" ht="20.1" customHeight="1"/>
-    <row r="143" ht="20.1" customHeight="1"/>
-    <row r="144" ht="20.1" customHeight="1"/>
-    <row r="145" ht="20.1" customHeight="1"/>
-    <row r="146" ht="20.1" customHeight="1"/>
-    <row r="147" ht="20.1" customHeight="1"/>
-    <row r="148" ht="20.1" customHeight="1"/>
-    <row r="149" ht="20.1" customHeight="1"/>
-    <row r="150" ht="20.1" customHeight="1"/>
-    <row r="151" ht="20.1" customHeight="1"/>
-    <row r="152" ht="20.1" customHeight="1"/>
-    <row r="153" ht="20.1" customHeight="1"/>
-    <row r="154" ht="20.1" customHeight="1"/>
-    <row r="155" ht="20.1" customHeight="1"/>
-    <row r="156" ht="20.1" customHeight="1"/>
-    <row r="157" ht="20.1" customHeight="1"/>
-    <row r="158" ht="20.1" customHeight="1"/>
-    <row r="159" ht="20.1" customHeight="1"/>
-    <row r="160" ht="20.1" customHeight="1"/>
-    <row r="161" ht="20.1" customHeight="1"/>
-    <row r="162" ht="20.1" customHeight="1"/>
-    <row r="163" ht="20.1" customHeight="1"/>
-    <row r="164" ht="20.1" customHeight="1"/>
-    <row r="165" ht="20.1" customHeight="1"/>
-    <row r="166" ht="20.1" customHeight="1"/>
-    <row r="167" ht="20.1" customHeight="1"/>
-    <row r="168" ht="20.1" customHeight="1"/>
-    <row r="169" ht="20.1" customHeight="1"/>
-    <row r="170" ht="20.1" customHeight="1"/>
-    <row r="171" ht="20.1" customHeight="1"/>
-    <row r="172" ht="20.1" customHeight="1"/>
-    <row r="173" ht="20.1" customHeight="1"/>
-    <row r="174" ht="20.1" customHeight="1"/>
-    <row r="175" ht="20.1" customHeight="1"/>
-    <row r="176" ht="20.1" customHeight="1"/>
-    <row r="177" ht="20.1" customHeight="1"/>
-    <row r="178" ht="20.1" customHeight="1"/>
-    <row r="179" ht="20.1" customHeight="1"/>
-    <row r="180" ht="20.1" customHeight="1"/>
-    <row r="181" ht="20.1" customHeight="1"/>
-    <row r="182" ht="20.1" customHeight="1"/>
-    <row r="183" ht="20.1" customHeight="1"/>
-    <row r="184" ht="20.1" customHeight="1"/>
-    <row r="185" ht="20.1" customHeight="1"/>
-    <row r="186" ht="20.1" customHeight="1"/>
-    <row r="187" ht="20.1" customHeight="1"/>
-    <row r="188" ht="20.1" customHeight="1"/>
-    <row r="189" ht="20.1" customHeight="1"/>
-    <row r="190" ht="20.1" customHeight="1"/>
-    <row r="191" ht="20.1" customHeight="1"/>
-    <row r="192" ht="20.1" customHeight="1"/>
-    <row r="193" ht="20.1" customHeight="1"/>
-    <row r="194" ht="20.1" customHeight="1"/>
-    <row r="195" ht="20.1" customHeight="1"/>
-    <row r="196" ht="20.1" customHeight="1"/>
-    <row r="197" ht="20.1" customHeight="1"/>
-    <row r="198" ht="20.1" customHeight="1"/>
+    <row r="142" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>